--- a/data/trans_orig/P23_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P23_R-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2007</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>186812</t>
+          <t>183681</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>230525</t>
+          <t>228896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151451</t>
+          <t>149812</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>192196</t>
+          <t>189078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>346097</t>
+          <t>345469</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>404483</t>
+          <t>405192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,19%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262497</t>
+          <t>264126</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>306210</t>
+          <t>309341</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275293</t>
+          <t>278411</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>316038</t>
+          <t>317677</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>556028</t>
+          <t>555319</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>614414</t>
+          <t>615042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,03%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>372038</t>
+          <t>372735</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>425464</t>
+          <t>426928</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>211202</t>
+          <t>210158</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>259601</t>
+          <t>257342</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>600039</t>
+          <t>595668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>675295</t>
+          <t>670585</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,27%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>310025</t>
+          <t>308561</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363451</t>
+          <t>362754</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>365893</t>
+          <t>368152</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>414292</t>
+          <t>415336</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>685687</t>
+          <t>690397</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>760943</t>
+          <t>765314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>56,23%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>317087</t>
+          <t>314486</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>367317</t>
+          <t>365658</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>233501</t>
+          <t>231949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>285075</t>
+          <t>287484</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>562393</t>
+          <t>560629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>633562</t>
+          <t>631987</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,57%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>271351</t>
+          <t>273010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321581</t>
+          <t>324182</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>404669</t>
+          <t>402260</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456243</t>
+          <t>457795</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>694850</t>
+          <t>696425</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>766019</t>
+          <t>767783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>213044</t>
+          <t>210904</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>259258</t>
+          <t>258605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126093</t>
+          <t>124076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>166612</t>
+          <t>164904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>349117</t>
+          <t>350197</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>413668</t>
+          <t>410189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>259889</t>
+          <t>260542</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>306103</t>
+          <t>308243</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349030</t>
+          <t>350738</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>389549</t>
+          <t>391566</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>621121</t>
+          <t>624600</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>685672</t>
+          <t>684592</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,16%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109848</t>
+          <t>113224</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>148107</t>
+          <t>148358</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35857</t>
+          <t>35575</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61454</t>
+          <t>62900</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>152935</t>
+          <t>153621</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>201462</t>
+          <t>201060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>238603</t>
+          <t>238352</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>276862</t>
+          <t>273486</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>342532</t>
+          <t>341086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>368129</t>
+          <t>368411</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>589234</t>
+          <t>589636</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>637761</t>
+          <t>637075</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,57%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41938</t>
+          <t>40946</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66669</t>
+          <t>66732</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47755</t>
+          <t>48053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75126</t>
+          <t>76143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225914</t>
+          <t>225851</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250645</t>
+          <t>251637</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>328811</t>
+          <t>329583</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>340108</t>
+          <t>340101</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>560391</t>
+          <t>559374</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>587762</t>
+          <t>587464</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15017</t>
+          <t>15410</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32851</t>
+          <t>32477</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>11607</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>18099</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>37871</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177032</t>
+          <t>177406</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>194866</t>
+          <t>194473</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>323207</t>
+          <t>322301</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>332778</t>
+          <t>332793</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>505265</t>
+          <t>505920</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>525423</t>
+          <t>525692</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1325414</t>
+          <t>1329366</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1442511</t>
+          <t>1446641</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>814610</t>
+          <t>815961</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>918767</t>
+          <t>910974</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2170312</t>
+          <t>2166858</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2328069</t>
+          <t>2330261</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1832990</t>
+          <t>1828860</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1950087</t>
+          <t>1946135</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2460430</t>
+          <t>2468223</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2564587</t>
+          <t>2563236</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4326629</t>
+          <t>4324437</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4484386</t>
+          <t>4487840</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,44%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2012</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>145629</t>
+          <t>146372</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>187643</t>
+          <t>187477</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>130602</t>
+          <t>128806</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>170022</t>
+          <t>167835</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>287151</t>
+          <t>288172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>343744</t>
+          <t>344351</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266503</t>
+          <t>266669</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308517</t>
+          <t>307774</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259212</t>
+          <t>261399</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298632</t>
+          <t>300428</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>539636</t>
+          <t>539029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>596229</t>
+          <t>595208</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,38%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>322158</t>
+          <t>321799</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>374929</t>
+          <t>376728</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>226740</t>
+          <t>224948</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>272211</t>
+          <t>272853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>561726</t>
+          <t>560404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>636282</t>
+          <t>634612</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,92%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>312158</t>
+          <t>310359</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364929</t>
+          <t>365288</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>338044</t>
+          <t>337402</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>383515</t>
+          <t>385307</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>661060</t>
+          <t>662730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>735616</t>
+          <t>736938</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>299150</t>
+          <t>300014</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>350009</t>
+          <t>352230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>223987</t>
+          <t>221537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>275197</t>
+          <t>276138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>538582</t>
+          <t>536913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>610567</t>
+          <t>612046</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>330824</t>
+          <t>328603</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>381683</t>
+          <t>380819</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>434667</t>
+          <t>433726</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>485877</t>
+          <t>488327</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>780130</t>
+          <t>778651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>852115</t>
+          <t>853784</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,39%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>255941</t>
+          <t>252975</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>311998</t>
+          <t>306570</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>215977</t>
+          <t>216178</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>267391</t>
+          <t>268361</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>482263</t>
+          <t>484219</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>558525</t>
+          <t>556558</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302619</t>
+          <t>308047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358676</t>
+          <t>361642</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348808</t>
+          <t>347838</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>400222</t>
+          <t>400021</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>672291</t>
+          <t>674258</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>748553</t>
+          <t>746597</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,66%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136621</t>
+          <t>135475</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>178559</t>
+          <t>177482</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52747</t>
+          <t>53366</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85471</t>
+          <t>85060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>198465</t>
+          <t>196115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>251835</t>
+          <t>254089</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>250870</t>
+          <t>251947</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>292808</t>
+          <t>293954</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>362329</t>
+          <t>362740</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>395053</t>
+          <t>394434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>625394</t>
+          <t>623140</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>678764</t>
+          <t>681114</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,64%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37554</t>
+          <t>39213</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66987</t>
+          <t>68496</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29630</t>
+          <t>30472</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54166</t>
+          <t>54010</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88616</t>
+          <t>90789</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>242799</t>
+          <t>241290</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272232</t>
+          <t>270573</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>324366</t>
+          <t>323524</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>342483</t>
+          <t>342679</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>575166</t>
+          <t>572993</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>609616</t>
+          <t>609772</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17630</t>
+          <t>17695</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38738</t>
+          <t>38070</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11236</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21035</t>
+          <t>21474</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45472</t>
+          <t>44440</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>211113</t>
+          <t>211781</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>232221</t>
+          <t>232156</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>377743</t>
+          <t>376090</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>593358</t>
+          <t>594390</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>617795</t>
+          <t>617356</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1296941</t>
+          <t>1297780</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1415781</t>
+          <t>1415261</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>920492</t>
+          <t>921956</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1029014</t>
+          <t>1029669</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2245409</t>
+          <t>2252453</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2417827</t>
+          <t>2413925</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2009968</t>
+          <t>2010488</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2128808</t>
+          <t>2127969</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2527313</t>
+          <t>2526658</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2635835</t>
+          <t>2634371</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4564249</t>
+          <t>4568151</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4736667</t>
+          <t>4729623</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,74%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2016</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>126605</t>
+          <t>126347</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>165208</t>
+          <t>165473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90812</t>
+          <t>90995</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>123967</t>
+          <t>124623</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>227263</t>
+          <t>225211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>282569</t>
+          <t>280220</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>254255</t>
+          <t>253990</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292858</t>
+          <t>293116</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271788</t>
+          <t>271132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304943</t>
+          <t>304760</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>532649</t>
+          <t>534998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>587955</t>
+          <t>590007</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>244748</t>
+          <t>246258</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>293458</t>
+          <t>295575</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>191061</t>
+          <t>190593</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>235565</t>
+          <t>236277</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>451560</t>
+          <t>451640</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>516842</t>
+          <t>515961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297038</t>
+          <t>294921</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>345748</t>
+          <t>344238</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327979</t>
+          <t>327267</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372483</t>
+          <t>372951</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>637198</t>
+          <t>638079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>702480</t>
+          <t>702400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,86%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>242667</t>
+          <t>241705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>295029</t>
+          <t>292468</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>198589</t>
+          <t>197920</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>244723</t>
+          <t>245906</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>454501</t>
+          <t>452934</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>528498</t>
+          <t>525224</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>372996</t>
+          <t>375557</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>425358</t>
+          <t>426320</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>415736</t>
+          <t>414553</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>461870</t>
+          <t>462539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>799985</t>
+          <t>803259</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>873982</t>
+          <t>875549</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,91%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>253205</t>
+          <t>250782</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>304927</t>
+          <t>304513</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>205606</t>
+          <t>205357</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>256156</t>
+          <t>254014</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>474020</t>
+          <t>472457</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>550508</t>
+          <t>544996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,15%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341121</t>
+          <t>341535</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>392843</t>
+          <t>395266</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>390805</t>
+          <t>392947</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>441355</t>
+          <t>441604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>742501</t>
+          <t>748013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>818989</t>
+          <t>820552</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,46%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>126011</t>
+          <t>125451</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>169646</t>
+          <t>168060</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95907</t>
+          <t>95243</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>136149</t>
+          <t>133819</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>232382</t>
+          <t>233352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>292545</t>
+          <t>289122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>308272</t>
+          <t>309858</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>351907</t>
+          <t>352467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>359591</t>
+          <t>361921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399833</t>
+          <t>400497</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>681113</t>
+          <t>684536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>741276</t>
+          <t>740306</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,03%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45592</t>
+          <t>43907</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72535</t>
+          <t>74340</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20451</t>
+          <t>19593</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43407</t>
+          <t>41574</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71407</t>
+          <t>72234</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106354</t>
+          <t>110461</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261795</t>
+          <t>259990</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288738</t>
+          <t>290423</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>334355</t>
+          <t>336188</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>357311</t>
+          <t>358169</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>605738</t>
+          <t>601631</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>640685</t>
+          <t>639858</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17213</t>
+          <t>17286</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33697</t>
+          <t>33638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>16517</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22126</t>
+          <t>23001</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44301</t>
+          <t>45231</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>222436</t>
+          <t>222495</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>238920</t>
+          <t>238847</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>382643</t>
+          <t>382367</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>396114</t>
+          <t>396116</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>610716</t>
+          <t>609786</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>632891</t>
+          <t>632016</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1133536</t>
+          <t>1132509</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1249039</t>
+          <t>1247052</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>873361</t>
+          <t>871670</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>978159</t>
+          <t>977404</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2029989</t>
+          <t>2032585</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2191972</t>
+          <t>2190225</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2143375</t>
+          <t>2145362</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2258878</t>
+          <t>2259905</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2560944</t>
+          <t>2561699</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2665742</t>
+          <t>2667433</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4739545</t>
+          <t>4741292</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4901528</t>
+          <t>4898932</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P23_R-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>183681</t>
+          <t>184614</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>228896</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>149812</t>
+          <t>149109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>189078</t>
+          <t>187624</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>345469</t>
+          <t>345174</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>405192</t>
+          <t>405154</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264126</t>
+          <t>263159</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309341</t>
+          <t>308408</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278411</t>
+          <t>279865</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>317677</t>
+          <t>318380</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>555319</t>
+          <t>555357</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>615042</t>
+          <t>615337</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,06%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>372735</t>
+          <t>368895</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>426928</t>
+          <t>425481</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>210158</t>
+          <t>206673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>257342</t>
+          <t>260646</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>595668</t>
+          <t>591984</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>670585</t>
+          <t>667771</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,07%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>308561</t>
+          <t>310008</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362754</t>
+          <t>366594</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>368152</t>
+          <t>364848</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>415336</t>
+          <t>418821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>690397</t>
+          <t>693211</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>765314</t>
+          <t>768998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,5%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>314486</t>
+          <t>312294</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>365658</t>
+          <t>368691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>231949</t>
+          <t>232278</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>287484</t>
+          <t>284485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>560629</t>
+          <t>561652</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>631987</t>
+          <t>634996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,8%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273010</t>
+          <t>269977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324182</t>
+          <t>326374</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>402260</t>
+          <t>405259</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457795</t>
+          <t>457466</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>696425</t>
+          <t>693416</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>767783</t>
+          <t>766760</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>210904</t>
+          <t>214743</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258605</t>
+          <t>258844</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124076</t>
+          <t>125659</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164904</t>
+          <t>167436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>350197</t>
+          <t>349842</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>410189</t>
+          <t>412491</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>260542</t>
+          <t>260303</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>308243</t>
+          <t>304404</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>350738</t>
+          <t>348206</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>391566</t>
+          <t>389983</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>624600</t>
+          <t>622298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>684592</t>
+          <t>684947</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,19%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>113224</t>
+          <t>110144</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>148358</t>
+          <t>146628</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35575</t>
+          <t>33863</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62900</t>
+          <t>61300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>153621</t>
+          <t>153889</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>201060</t>
+          <t>199316</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>238352</t>
+          <t>240082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>273486</t>
+          <t>276566</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>341086</t>
+          <t>342686</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>368411</t>
+          <t>370123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>589636</t>
+          <t>591380</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>637075</t>
+          <t>636807</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,54%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40946</t>
+          <t>41452</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66732</t>
+          <t>65864</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13136</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48053</t>
+          <t>47497</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76143</t>
+          <t>76448</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225851</t>
+          <t>226719</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251637</t>
+          <t>251131</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>329583</t>
+          <t>329798</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>340101</t>
+          <t>340115</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>559374</t>
+          <t>559069</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>587464</t>
+          <t>588020</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15410</t>
+          <t>14578</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32477</t>
+          <t>31956</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11607</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37871</t>
+          <t>39712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177406</t>
+          <t>177927</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>194473</t>
+          <t>195305</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>322301</t>
+          <t>322697</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>332793</t>
+          <t>332779</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>505920</t>
+          <t>504079</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>525692</t>
+          <t>525052</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1329366</t>
+          <t>1331274</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1446641</t>
+          <t>1442553</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>815961</t>
+          <t>815438</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>910974</t>
+          <t>919173</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2166858</t>
+          <t>2173732</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2330261</t>
+          <t>2325182</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1828860</t>
+          <t>1832948</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1946135</t>
+          <t>1944227</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2468223</t>
+          <t>2460024</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2563236</t>
+          <t>2563759</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4324437</t>
+          <t>4329516</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4487840</t>
+          <t>4480966</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>146372</t>
+          <t>144723</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>187477</t>
+          <t>186619</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128806</t>
+          <t>129226</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167835</t>
+          <t>168384</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>288172</t>
+          <t>286078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>344351</t>
+          <t>341992</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266669</t>
+          <t>267527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307774</t>
+          <t>309423</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261399</t>
+          <t>260850</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300428</t>
+          <t>300008</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>539029</t>
+          <t>541388</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>595208</t>
+          <t>597302</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,62%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>321799</t>
+          <t>322456</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>376728</t>
+          <t>373900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>224948</t>
+          <t>225119</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>272853</t>
+          <t>273326</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>560404</t>
+          <t>558386</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>634612</t>
+          <t>633092</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>310359</t>
+          <t>313187</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365288</t>
+          <t>364631</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337402</t>
+          <t>336929</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>385307</t>
+          <t>385136</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>662730</t>
+          <t>664250</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736938</t>
+          <t>738956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,96%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>300014</t>
+          <t>297948</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>352230</t>
+          <t>349009</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>221537</t>
+          <t>222220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>276138</t>
+          <t>273674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>536913</t>
+          <t>540568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>612046</t>
+          <t>611768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,99%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>328603</t>
+          <t>331824</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>380819</t>
+          <t>382885</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>433726</t>
+          <t>436190</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>488327</t>
+          <t>487644</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>778651</t>
+          <t>778929</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>853784</t>
+          <t>850129</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,13%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>252975</t>
+          <t>254439</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>306570</t>
+          <t>306001</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>216178</t>
+          <t>213943</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>268361</t>
+          <t>264395</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>484219</t>
+          <t>484378</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>556558</t>
+          <t>556061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>308047</t>
+          <t>308616</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361642</t>
+          <t>360178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347838</t>
+          <t>351804</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>400021</t>
+          <t>402256</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>674258</t>
+          <t>674755</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>746597</t>
+          <t>746438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,65%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>135475</t>
+          <t>136759</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>177482</t>
+          <t>180272</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53366</t>
+          <t>53185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85060</t>
+          <t>85499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>196115</t>
+          <t>196655</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>254089</t>
+          <t>252701</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>251947</t>
+          <t>249157</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>293954</t>
+          <t>292670</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>362740</t>
+          <t>362301</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>394434</t>
+          <t>394615</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>623140</t>
+          <t>624528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>681114</t>
+          <t>680574</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,58%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39213</t>
+          <t>38541</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68496</t>
+          <t>66479</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11356</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>30601</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54010</t>
+          <t>55994</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90789</t>
+          <t>89249</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>241290</t>
+          <t>243307</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270573</t>
+          <t>271245</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>323524</t>
+          <t>323395</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>342679</t>
+          <t>342640</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>572993</t>
+          <t>574533</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>609772</t>
+          <t>607788</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17695</t>
+          <t>18278</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38070</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21474</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44440</t>
+          <t>45497</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>211781</t>
+          <t>211244</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>232156</t>
+          <t>231573</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>376090</t>
+          <t>377073</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387970</t>
+          <t>387973</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>594390</t>
+          <t>593333</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>617356</t>
+          <t>618284</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1297780</t>
+          <t>1296778</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1415261</t>
+          <t>1414730</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>921956</t>
+          <t>920335</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1029669</t>
+          <t>1033648</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2252453</t>
+          <t>2253291</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2413925</t>
+          <t>2411864</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2010488</t>
+          <t>2011019</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2127969</t>
+          <t>2128971</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2526658</t>
+          <t>2522679</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2634371</t>
+          <t>2635992</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4568151</t>
+          <t>4570212</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4729623</t>
+          <t>4728785</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>126347</t>
+          <t>125719</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>165473</t>
+          <t>164573</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90995</t>
+          <t>90352</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124623</t>
+          <t>124750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>225211</t>
+          <t>226507</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>280220</t>
+          <t>279848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253990</t>
+          <t>254890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293116</t>
+          <t>293744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271132</t>
+          <t>271005</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304760</t>
+          <t>305403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>534998</t>
+          <t>535370</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>590007</t>
+          <t>588711</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,22%</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>246258</t>
+          <t>244337</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>295575</t>
+          <t>293556</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>190593</t>
+          <t>193039</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>236277</t>
+          <t>239245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>451640</t>
+          <t>449674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>515961</t>
+          <t>517690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>294921</t>
+          <t>296940</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>344238</t>
+          <t>346159</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327267</t>
+          <t>324299</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372951</t>
+          <t>370505</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>638079</t>
+          <t>636350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>702400</t>
+          <t>704366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,03%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>241705</t>
+          <t>243522</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>292468</t>
+          <t>294247</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>197920</t>
+          <t>197257</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>245906</t>
+          <t>245724</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>452934</t>
+          <t>451699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>525224</t>
+          <t>524655</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>375557</t>
+          <t>373778</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>426320</t>
+          <t>424503</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>414553</t>
+          <t>414735</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>462539</t>
+          <t>463202</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>803259</t>
+          <t>803828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>875549</t>
+          <t>876784</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,0%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>250782</t>
+          <t>249750</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>304513</t>
+          <t>305086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>205357</t>
+          <t>205186</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>254014</t>
+          <t>254108</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>472457</t>
+          <t>471895</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>544996</t>
+          <t>544464</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341535</t>
+          <t>340962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>395266</t>
+          <t>396298</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>392947</t>
+          <t>392853</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>441604</t>
+          <t>441775</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>748013</t>
+          <t>748545</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>820552</t>
+          <t>821114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,5%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125451</t>
+          <t>125185</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168060</t>
+          <t>168245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95243</t>
+          <t>94486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133819</t>
+          <t>133653</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>233352</t>
+          <t>231726</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>289122</t>
+          <t>291316</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>309858</t>
+          <t>309673</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>352467</t>
+          <t>352733</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>361921</t>
+          <t>362087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>400497</t>
+          <t>401254</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>684536</t>
+          <t>682342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>740306</t>
+          <t>741932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,2%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43907</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74340</t>
+          <t>72489</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19593</t>
+          <t>20819</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41574</t>
+          <t>41477</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72234</t>
+          <t>72358</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>110461</t>
+          <t>110091</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259990</t>
+          <t>261841</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290423</t>
+          <t>290127</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>336188</t>
+          <t>336285</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>358169</t>
+          <t>356943</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>601631</t>
+          <t>602001</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>639858</t>
+          <t>639734</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17286</t>
+          <t>17320</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33638</t>
+          <t>34166</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16517</t>
+          <t>17157</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23001</t>
+          <t>23141</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45231</t>
+          <t>44968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>222495</t>
+          <t>221967</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>238847</t>
+          <t>238813</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>382367</t>
+          <t>381727</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>396116</t>
+          <t>396160</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>609786</t>
+          <t>610049</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>632016</t>
+          <t>631876</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1132509</t>
+          <t>1141425</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1247052</t>
+          <t>1252088</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>871670</t>
+          <t>871656</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>977404</t>
+          <t>984620</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2032585</t>
+          <t>2034452</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2190225</t>
+          <t>2193205</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2145362</t>
+          <t>2140326</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2259905</t>
+          <t>2250989</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2561699</t>
+          <t>2554483</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2667433</t>
+          <t>2667447</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4741292</t>
+          <t>4738312</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4898932</t>
+          <t>4897065</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>
